--- a/Data/Output/capitals_population_demo.xlsx
+++ b/Data/Output/capitals_population_demo.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3506730</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="9">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Kyiv» описує кілька об'єктів, узято найвідоміший; інші варіанти: 17 (Q4512420)</t>
+          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -1802,11 +1802,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «London» описує кілька об'єктів, узято найвідоміший; інші варіанти: 422324 (Q92561), 10279 (Q1001456)</t>
+          <t>[wikidata_lookup] Назва «London» неоднозначна; інші кандидати: 936 (Q79348), 422324 (Q92561); підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>5746</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1849,11 +1849,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Paris» описує кілька об'єктів, узято найвідоміший; інші варіанти: 24476 (Q830149), 541 (Q984459)</t>
+          <t>[wikidata_lookup] Назва «Paris» неоднозначна; інші кандидати: 3176 (Q79917), 8291 (Q576584); контрольне значення відкинуто (Значення 2.1 менше за нижню межу 1000)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>35</v>
+        <v>7662</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1896,11 +1896,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Berlin» описує кілька об'єктів, узято найвідоміший; інші варіанти: 9425 (Q821244), 121 (Q1930098)</t>
+          <t>[wikidata_lookup] Назва «Berlin» неоднозначна; інші кандидати: 9425 (Q821244), 121 (Q1930098); підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>34</v>
+        <v>9271</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1943,11 +1943,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Warsaw» описує кілька об'єктів, узято найвідоміший; інші варіанти: 15804 (Q992560), 2209 (Q967161)</t>
+          <t>[wikidata_lookup] Назва «Warsaw» неоднозначна; інші кандидати: 1510 (Q576165), 2209 (Q967161); контрольне значення відкинуто (Значення 1.86 менше за нижню межу 1000)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>35</v>
+        <v>6841</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1990,11 +1990,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Rome» описує кілька об'єктів, узято найвідоміший; інші варіанти: 37713 (Q6580), 32127 (Q6586)</t>
+          <t>[wikidata_lookup] Назва «Rome» неоднозначна; інші кандидати: 114 (Q1925709), 37713 (Q6580); підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>11977</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3506730</v>
+        <v>2802</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q2807</t>
+          <t>http://www.wikidata.org/entity/Q1934324</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2032,16 +2032,16 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>ambiguous</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Madrid» описує кілька об'єктів, узято найвідоміший; інші варіанти: 2802 (Q1934324), 265 (Q66470)</t>
+          <t>[wikidata_lookup] Назва «Madrid» неоднозначна; інші кандидати: 3332035 (Q116170766); розбіжність джерел: 2802.0 проти 3400000.0 (llm_knowledge)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>33</v>
+        <v>9214</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2084,11 +2084,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Vienna» описує кілька об'єктів, узято найвідоміший; інші варіанти: 581 (Q952461), 1343 (Q577544)</t>
+          <t>[wikidata_lookup] Назва «Vienna» неоднозначна; інші кандидати: 1343 (Q577544), 10652 (Q749045); контрольне значення відкинуто (Значення 2 менше за нижню межу 1000)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>9152</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2131,11 +2131,11 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Stockholm» описує кілька об'єктів, узято найвідоміший; інші варіанти: 102 (Q1787199), 78 (Q976601)</t>
+          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2178,11 +2178,11 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Athens» описує кілька об'єктів, узято найвідоміший; інші варіанти: 127315 (Q203263), 23849 (Q755420)</t>
+          <t>[wikidata_lookup] Назва «Athens» неоднозначна; інші кандидати: 25406 (Q79439), 127315 (Q203263); підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>5710</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Output/capitals_population_demo.xlsx
+++ b/Data/Output/capitals_population_demo.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2802</v>
+        <v>3506730</v>
       </c>
     </row>
     <row r="9">
@@ -1730,6 +1730,11 @@
       <c r="C2" t="n">
         <v>2952301</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>wikidata_lookup</t>
@@ -1759,7 +1764,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1777,6 +1782,11 @@
       <c r="C3" t="n">
         <v>8799728</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>wikidata_lookup</t>
@@ -1797,16 +1807,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>ambiguous</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «London» неоднозначна; інші кандидати: 936 (Q79348), 422324 (Q92561); підтверджено через llm_knowledge</t>
+          <t>[wikidata_lookup] Назва «London» неоднозначна; інші кандидати: 936 (Q79348), 422324 (Q92561); розбіжність джерел: 8799728.0 проти 8583.0 (llm_knowledge)</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5746</v>
+        <v>7110</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1824,6 +1834,11 @@
       <c r="C4" t="n">
         <v>2103778</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>wikidata_lookup</t>
@@ -1849,11 +1864,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Paris» неоднозначна; інші кандидати: 3176 (Q79917), 8291 (Q576584); контрольне значення відкинуто (Значення 2.1 менше за нижню межу 1000)</t>
+          <t>[wikidata_lookup] Назва «Paris» неоднозначна; інші кандидати: 3176 (Q79917), 8291 (Q576584); підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7662</v>
+        <v>9942</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1871,6 +1886,11 @@
       <c r="C5" t="n">
         <v>3782202</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>wikidata_lookup</t>
@@ -1900,7 +1920,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9271</v>
+        <v>6331</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1918,6 +1938,11 @@
       <c r="C6" t="n">
         <v>1862402</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>wikidata_lookup</t>
@@ -1943,11 +1968,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Warsaw» неоднозначна; інші кандидати: 1510 (Q576165), 2209 (Q967161); контрольне значення відкинуто (Значення 1.86 менше за нижню межу 1000)</t>
+          <t>[wikidata_lookup] Назва «Warsaw» неоднозначна; інші кандидати: 1510 (Q576165), 2209 (Q967161); підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6841</v>
+        <v>9614</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1965,6 +1990,11 @@
       <c r="C7" t="n">
         <v>2748109</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>wikidata_lookup</t>
@@ -1985,16 +2015,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>ambiguous</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Rome» неоднозначна; інші кандидати: 114 (Q1925709), 37713 (Q6580); підтверджено через llm_knowledge</t>
+          <t>[wikidata_lookup] Назва «Rome» неоднозначна; інші кандидати: 114 (Q1925709), 37713 (Q6580); розбіжність джерел: 2748109.0 проти 2.8 (llm_knowledge)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>11977</v>
+        <v>9119</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2010,7 +2040,12 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2802</v>
+        <v>3506730</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2019,7 +2054,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q1934324</t>
+          <t>http://www.wikidata.org/entity/Q2807</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2032,16 +2067,16 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ambiguous</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Madrid» неоднозначна; інші кандидати: 3332035 (Q116170766); розбіжність джерел: 2802.0 проти 3400000.0 (llm_knowledge)</t>
+          <t>[wikidata_lookup] Назва «Madrid» неоднозначна; інші кандидати: 2802 (Q1934324), 265 (Q66470); підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>9214</v>
+        <v>9625</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2059,6 +2094,11 @@
       <c r="C9" t="n">
         <v>2028289</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>wikidata_lookup</t>
@@ -2084,11 +2124,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Vienna» неоднозначна; інші кандидати: 1343 (Q577544), 10652 (Q749045); контрольне значення відкинуто (Значення 2 менше за нижню межу 1000)</t>
+          <t>[wikidata_lookup] Назва «Vienna» неоднозначна; інші кандидати: 1343 (Q577544), 10652 (Q749045); підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>9152</v>
+        <v>5571</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2106,6 +2146,11 @@
       <c r="C10" t="n">
         <v>984748</v>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>wikidata_lookup</t>
@@ -2153,6 +2198,11 @@
       <c r="C11" t="n">
         <v>643452</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>wikidata_lookup</t>
@@ -2182,7 +2232,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>5710</v>
+        <v>4216</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Output/capitals_population_demo.xlsx
+++ b/Data/Output/capitals_population_demo.xlsx
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1807,16 +1807,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ambiguous</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «London» неоднозначна; інші кандидати: 936 (Q79348), 422324 (Q92561); розбіжність джерел: 8799728.0 проти 8583.0 (llm_knowledge)</t>
+          <t>[wikidata_lookup] Назва «London» неоднозначна; інші кандидати: 936 (Q79348), 422324 (Q92561); підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7110</v>
+        <v>5950</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9942</v>
+        <v>6554</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6331</v>
+        <v>4794</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>9614</v>
+        <v>5459</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2015,16 +2015,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ambiguous</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Rome» неоднозначна; інші кандидати: 114 (Q1925709), 37713 (Q6580); розбіжність джерел: 2748109.0 проти 2.8 (llm_knowledge)</t>
+          <t>[wikidata_lookup] Назва «Rome» неоднозначна; інші кандидати: 114 (Q1925709), 37713 (Q6580); підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>9119</v>
+        <v>6988</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>9625</v>
+        <v>9123</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5571</v>
+        <v>5338</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>4216</v>
+        <v>5671</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Output/capitals_population_demo.xlsx
+++ b/Data/Output/capitals_population_demo.xlsx
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1807,16 +1807,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>ambiguous</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «London» неоднозначна; інші кандидати: 936 (Q79348), 422324 (Q92561); підтверджено через llm_knowledge</t>
+          <t>[wikidata_lookup] Назва «London» неоднозначна; інші кандидати: 936 (Q79348), 422324 (Q92561); розбіжність джерел: 8799728.0 проти 8600.0 (llm_knowledge)</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5950</v>
+        <v>4331</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6554</v>
+        <v>5590</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4794</v>
+        <v>6870</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5459</v>
+        <v>3655</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6988</v>
+        <v>4474</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>9123</v>
+        <v>8350</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5338</v>
+        <v>4728</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>5671</v>
+        <v>3069</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Output/capitals_population_demo.xlsx
+++ b/Data/Output/capitals_population_demo.xlsx
@@ -1641,20 +1641,6 @@
   </sheetPr>
   <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="4" min="1" max="1"/>
-    <col width="16" customWidth="1" style="4" min="2" max="2"/>
-    <col width="12" customWidth="1" style="4" min="3" max="3"/>
-    <col width="8" customWidth="1" style="4" min="4" max="4"/>
-    <col width="20" customWidth="1" style="4" min="5" max="5"/>
-    <col width="46" customWidth="1" style="4" min="6" max="6"/>
-    <col width="40" customWidth="1" style="4" min="7" max="7"/>
-    <col width="8" customWidth="1" style="4" min="8" max="8"/>
-    <col width="14" customWidth="1" style="4" min="9" max="9"/>
-    <col width="60" customWidth="1" style="4" min="10" max="10"/>
-    <col width="12" customWidth="1" style="4" min="11" max="11"/>
-    <col width="10" customWidth="1" style="4" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
@@ -1764,7 +1750,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1807,16 +1793,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ambiguous</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «London» неоднозначна; інші кандидати: 936 (Q79348), 422324 (Q92561); розбіжність джерел: 8799728.0 проти 8600.0 (llm_knowledge)</t>
+          <t>[wikidata_lookup] Назва «London» неоднозначна; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4331</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1864,11 +1850,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Paris» неоднозначна; інші кандидати: 3176 (Q79917), 8291 (Q576584); підтверджено через llm_knowledge</t>
+          <t>[wikidata_lookup] Назва «Paris» неоднозначна; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5590</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1916,11 +1902,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Berlin» неоднозначна; інші кандидати: 9425 (Q821244), 121 (Q1930098); підтверджено через llm_knowledge</t>
+          <t>[wikidata_lookup] Назва «Berlin» неоднозначна; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6870</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1968,11 +1954,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Warsaw» неоднозначна; інші кандидати: 1510 (Q576165), 2209 (Q967161); підтверджено через llm_knowledge</t>
+          <t>[wikidata_lookup] Назва «Warsaw» неоднозначна; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3655</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2020,11 +2006,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Rome» неоднозначна; інші кандидати: 114 (Q1925709), 37713 (Q6580); підтверджено через llm_knowledge</t>
+          <t>[wikidata_lookup] Назва «Rome» неоднозначна; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4474</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2072,11 +2058,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Madrid» неоднозначна; інші кандидати: 2802 (Q1934324), 265 (Q66470); підтверджено через llm_knowledge</t>
+          <t>[wikidata_lookup] Назва «Madrid» неоднозначна; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8350</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2124,11 +2110,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Vienna» неоднозначна; інші кандидати: 1343 (Q577544), 10652 (Q749045); підтверджено через llm_knowledge</t>
+          <t>[wikidata_lookup] Назва «Vienna» неоднозначна; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4728</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2180,7 +2166,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2228,11 +2214,11 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «Athens» неоднозначна; інші кандидати: 25406 (Q79439), 127315 (Q203263); підтверджено через llm_knowledge</t>
+          <t>[wikidata_lookup] Назва «Athens» неоднозначна; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>3069</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
